--- a/examples/micro_workbooks/codegen_basics.xlsx
+++ b/examples/micro_workbooks/codegen_basics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Software\excel-grapher\examples\micro_workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C079A2DB-D95A-468B-B0BF-27721ADBA59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33FA935-2E7F-4CA6-8078-B66190100F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12015" yWindow="0" windowWidth="11985" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MyNamedRange">Sheet1!$C$7:$D$7</definedName>
+    <definedName name="MyNamedRange">Sheet1!$C$9:$D$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,12 +36,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Linear dependency</t>
   </si>
   <si>
     <t>Will cycle</t>
+  </si>
+  <si>
+    <t>Single cell, no dependencies</t>
+  </si>
+  <si>
+    <t>Multiple targets</t>
   </si>
 </sst>
 </file>
@@ -383,31 +389,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1">
+        <f>1+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C1">
-        <f>B1+1</f>
+      <c r="C2">
+        <f>B2+1</f>
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="B2">
-        <f ca="1">C2+1</f>
+      <c r="C3">
+        <f>B3+1</f>
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <f>C3+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <f ca="1">C4+1</f>
         <v>0</v>
       </c>
-      <c r="C2">
-        <f ca="1">B2+1</f>
+      <c r="C4">
+        <f ca="1">B4+1</f>
         <v>0</v>
       </c>
     </row>

--- a/examples/micro_workbooks/codegen_basics.xlsx
+++ b/examples/micro_workbooks/codegen_basics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\Software\excel-grapher\examples\micro_workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33FA935-2E7F-4CA6-8078-B66190100F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84513CB-EFAD-4D7C-B439-93FFCF4B1B26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12015" yWindow="0" windowWidth="11985" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MyNamedRange">Sheet1!$C$9:$D$9</definedName>
+    <definedName name="MyNamedRange">Sheet1!$C$10:$D$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Linear dependency</t>
   </si>
@@ -47,7 +47,10 @@
     <t>Single cell, no dependencies</t>
   </si>
   <si>
-    <t>Multiple targets</t>
+    <t>Multiple adjacent targets</t>
+  </si>
+  <si>
+    <t>Multiple non-adjacent targets</t>
   </si>
 </sst>
 </file>
@@ -389,10 +392,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -401,7 +407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -413,9 +419,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -424,21 +430,37 @@
         <f>B3+1</f>
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <f>C3+1</f>
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
         <v>1</v>
       </c>
-      <c r="B4">
-        <f ca="1">C4+1</f>
+      <c r="C4">
+        <f>B4+1</f>
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <f>C4+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5">
+        <f ca="1">C5+1</f>
         <v>0</v>
       </c>
-      <c r="C4">
-        <f ca="1">B4+1</f>
+      <c r="C5">
+        <f ca="1">B5+1</f>
         <v>0</v>
       </c>
     </row>
